--- a/Calendar.xlsx
+++ b/Calendar.xlsx
@@ -36,14 +36,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="7">
-    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="177" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="177" formatCode="m&quot;월&quot;\ d&quot;일&quot;;@"/>
+    <numFmt numFmtId="178" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -407,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E24"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -705,16 +704,135 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-10-06</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>세진팩</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -995,9 +1113,111 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-10-07</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-10-13</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-10-19</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-10-23</v>
+      </c>
+      <c r="C21" t="str">
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>오지인터팩코리아</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-10-26</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Calendar.xlsx
+++ b/Calendar.xlsx
@@ -1276,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1336,9 +1336,77 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>동진물류포장</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>직접 입력</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>동진물류포장</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-10-08</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>직접 입력</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>동진물류포장</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-10-15</v>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v>직접 입력</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>동진물류포장</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-10-22</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>직접 입력</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
